--- a/data_extactor/batch_10_fa/trimmed/batch_0057_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0057_fa_trim.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | حساسیت به مسئله | توجه انتخابی | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | مهارت دستی | حساسیت به مسئله | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نانوایان | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان مراکز و سلف‌سرویس‌ها | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا</t>
+          <t>نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>تولید مواد غذایی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | قدرت بالاتنه | چابکی دستی | مرتب‌سازی اطلاعات | تسهیم زمان و توجه هم‌زمان | توجه انتخابی</t>
+          <t>درک شفاهی | بینایی نزدیک | قدرت تنه | مهارت دستی | ترتیب‌دهی اطلاعات | تقسیم توجه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان رستوران | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا | پیش‌خدمتان و گارسون‌ها</t>
+          <t>سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان رستوران | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | تولید و فراوری | مدیریت و امور اداری | آموزش و تدریس</t>
+          <t>تولید مواد غذایی | خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | دقت کنترل | قدرت بالاتنه | دید نزدیک | حساسیت به مسئله</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | دقت کنترل | قدرت تنه | بینایی نزدیک | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>آشپزان رستوران | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان غذاهای فوری | آشپزان فست‌فود | کارگران آماده‌سازی غذا | سرآشپزان و آشپزان ارشد | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا</t>
+          <t>آشپزان رستوران | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان غذاهای فوری | آشپزان غذاهای فوری و فست‌فود | کارگران آماده‌سازی غذا | سرآشپزان و آشپزان ارشد | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی</t>
+          <t>خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | قدرت بالاتنه | درک شفاهی</t>
+          <t>بینایی نزدیک | قدرت تنه | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نانوایان | قصابان و خردکنندگان گوشت | آشپزان فست‌فود | آشپزان رستوران | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا</t>
+          <t>نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | آشپزان غذاهای فوری و فست‌فود | آشپزان رستوران | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | چابکی دستی | به‌خاطرسپاری</t>
+          <t>بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | مهارت دستی | حفظ کردن</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>باریستاها | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | مدیران خدمات پذیرایی و غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
+          <t>باریستاها | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | تولید مواد غذایی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | تولید مواد غذایی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>وضوح گفتار | تشخیص گفتار | دید نزدیک | بیان شفاهی | درک شفاهی</t>
+          <t>وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>باریستاها | صندوق‌داران | آشپزان فست‌فود | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | پیش‌خدمتان و گارسون‌ها</t>
+          <t>باریستاها | صندوق‌داران | آشپزان غذاهای فوری و فست‌فود | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | چابکی انگشتان | تسهیم زمان و توجه هم‌زمان</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | مهارت انگشتان | تقسیم توجه</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نانوایان | متصدیان بار و بارتندرها | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | متصدیان بار و نوشیدنی | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تسهیم زمان و توجه هم‌زمان | قدرت بالاتنه | استقامت جسمانی</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تقسیم توجه | قدرت تنه | استقامت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>باریستاها | متصدیان بار و بارتندرها | صندوق‌داران | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | مدیران خدمات پذیرایی و غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ</t>
+          <t>باریستاها | متصدیان بار و نوشیدنی | صندوق‌داران | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | تولید مواد غذایی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
+          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>باربران و چمدان‌برهای هتل و مسافربری | متصدیان بار و بارتندرها | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | نظافتچیان منازل و اماکن اقامتی | پیش‌خدمتان و گارسون‌ها</t>
+          <t>متصدیان حمل بار و خدمات هتل | متصدیان بار و نوشیدنی | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | خدمتکاران و نظافتچیان منازل و هتل‌ها | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | استقامت جسمانی | چابکی دستی | ثبات دست و بازو | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | استقامت | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>باریستاها | متصدیان بار و بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
+          <t>باریستاها | متصدیان بار و نوشیدنی | ظرف‌شویان | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
